--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/133.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/133.xlsx
@@ -426,13 +426,13 @@
         <v>-17.53107621703964</v>
       </c>
       <c r="E2">
-        <v>-17.07295137266787</v>
+        <v>-15.40722466453045</v>
       </c>
       <c r="F2">
-        <v>2.613380552046332</v>
+        <v>2.389136525904089</v>
       </c>
       <c r="G2">
-        <v>-10.10686825442106</v>
+        <v>-9.669866311600643</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.3930927403554</v>
       </c>
       <c r="E3">
-        <v>-17.54241827304305</v>
+        <v>-16.05443869818071</v>
       </c>
       <c r="F3">
-        <v>2.803076687287419</v>
+        <v>2.212651194002849</v>
       </c>
       <c r="G3">
-        <v>-9.5511435274713</v>
+        <v>-8.724741976139653</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-17.16113318351075</v>
       </c>
       <c r="E4">
-        <v>-18.17540836983522</v>
+        <v>-15.63430952211909</v>
       </c>
       <c r="F4">
-        <v>2.823722916434794</v>
+        <v>2.501484683276175</v>
       </c>
       <c r="G4">
-        <v>-9.864814406771707</v>
+        <v>-8.804046094532893</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.82531147954579</v>
       </c>
       <c r="E5">
-        <v>-18.34137241374233</v>
+        <v>-18.02902997601128</v>
       </c>
       <c r="F5">
-        <v>2.897651393665039</v>
+        <v>2.385340946464462</v>
       </c>
       <c r="G5">
-        <v>-8.429037427480871</v>
+        <v>-8.136034283982136</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.41431113574436</v>
       </c>
       <c r="E6">
-        <v>-19.83272117326639</v>
+        <v>-18.30051652124513</v>
       </c>
       <c r="F6">
-        <v>2.913799587815212</v>
+        <v>2.550381554328624</v>
       </c>
       <c r="G6">
-        <v>-8.196670236079425</v>
+        <v>-7.966243024363995</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.92531615084923</v>
       </c>
       <c r="E7">
-        <v>-19.91675153695272</v>
+        <v>-18.86329262854836</v>
       </c>
       <c r="F7">
-        <v>3.133035304640129</v>
+        <v>2.179663947288567</v>
       </c>
       <c r="G7">
-        <v>-8.116250463839451</v>
+        <v>-6.849086189954775</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.38323443271877</v>
       </c>
       <c r="E8">
-        <v>-21.57622442248554</v>
+        <v>-19.8104727804667</v>
       </c>
       <c r="F8">
-        <v>2.958665623085639</v>
+        <v>2.305758033342708</v>
       </c>
       <c r="G8">
-        <v>-7.200384729854537</v>
+        <v>-6.638949311849537</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.77839844501459</v>
       </c>
       <c r="E9">
-        <v>-21.89229832279891</v>
+        <v>-20.21485192392964</v>
       </c>
       <c r="F9">
-        <v>2.939642994047751</v>
+        <v>2.103886554015274</v>
       </c>
       <c r="G9">
-        <v>-6.612438463171054</v>
+        <v>-5.543363992174209</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.12902101488301</v>
       </c>
       <c r="E10">
-        <v>-22.43536198274676</v>
+        <v>-20.50529013288559</v>
       </c>
       <c r="F10">
-        <v>3.019240817782756</v>
+        <v>2.061596741367553</v>
       </c>
       <c r="G10">
-        <v>-5.14712810712438</v>
+        <v>-5.536110586897665</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.42233410942658</v>
       </c>
       <c r="E11">
-        <v>-23.15348739088312</v>
+        <v>-21.85070428903846</v>
       </c>
       <c r="F11">
-        <v>3.135951157897984</v>
+        <v>2.162263261625361</v>
       </c>
       <c r="G11">
-        <v>-5.295404131282797</v>
+        <v>-4.292686235075104</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.67552274533269</v>
       </c>
       <c r="E12">
-        <v>-24.19886297318378</v>
+        <v>-22.16365354228653</v>
       </c>
       <c r="F12">
-        <v>3.193308973602627</v>
+        <v>2.243917093254113</v>
       </c>
       <c r="G12">
-        <v>-4.9032004906998</v>
+        <v>-2.993502364734598</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.87408214671814</v>
       </c>
       <c r="E13">
-        <v>-25.35869120755431</v>
+        <v>-22.8295882874845</v>
       </c>
       <c r="F13">
-        <v>3.242865225107705</v>
+        <v>2.075433790463916</v>
       </c>
       <c r="G13">
-        <v>-3.695483683063817</v>
+        <v>-2.712595954636359</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.0320732348574</v>
       </c>
       <c r="E14">
-        <v>-25.60189743261025</v>
+        <v>-23.84831832872403</v>
       </c>
       <c r="F14">
-        <v>3.620143501977934</v>
+        <v>2.646215379158499</v>
       </c>
       <c r="G14">
-        <v>-3.032834956286679</v>
+        <v>-1.489792990977918</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.13722507307719</v>
       </c>
       <c r="E15">
-        <v>-27.15537232704554</v>
+        <v>-24.30922188475071</v>
       </c>
       <c r="F15">
-        <v>3.390206935043652</v>
+        <v>2.234419032613614</v>
       </c>
       <c r="G15">
-        <v>-2.451264800311831</v>
+        <v>-2.222628593733145</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.206067400582432</v>
       </c>
       <c r="E16">
-        <v>-27.17948192266237</v>
+        <v>-25.75998193174402</v>
       </c>
       <c r="F16">
-        <v>3.608900899587139</v>
+        <v>2.930572370987096</v>
       </c>
       <c r="G16">
-        <v>-2.711380984423446</v>
+        <v>-1.182994804217039</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.243120949280263</v>
       </c>
       <c r="E17">
-        <v>-28.82859818813966</v>
+        <v>-26.4481831836377</v>
       </c>
       <c r="F17">
-        <v>3.733875032912695</v>
+        <v>2.686039970415488</v>
       </c>
       <c r="G17">
-        <v>-1.679404486739675</v>
+        <v>0.3450603214354412</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.280628777735031</v>
       </c>
       <c r="E18">
-        <v>-29.87083553795301</v>
+        <v>-27.46113942051745</v>
       </c>
       <c r="F18">
-        <v>4.188055625989219</v>
+        <v>3.27885116182012</v>
       </c>
       <c r="G18">
-        <v>-1.237562526340846</v>
+        <v>-0.2317294067806992</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.345483572099732</v>
       </c>
       <c r="E19">
-        <v>-29.91690370403304</v>
+        <v>-27.3062520240331</v>
       </c>
       <c r="F19">
-        <v>4.25909807118811</v>
+        <v>3.655407102315109</v>
       </c>
       <c r="G19">
-        <v>-0.3989450619692869</v>
+        <v>0.9228961820419913</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.480771266189657</v>
       </c>
       <c r="E20">
-        <v>-30.03173674791954</v>
+        <v>-28.29646173597232</v>
       </c>
       <c r="F20">
-        <v>4.007499696670622</v>
+        <v>3.300128606928429</v>
       </c>
       <c r="G20">
-        <v>-0.4247011062648167</v>
+        <v>0.628360255958573</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.720211495695557</v>
       </c>
       <c r="E21">
-        <v>-31.12691195888256</v>
+        <v>-29.08080249104884</v>
       </c>
       <c r="F21">
-        <v>4.225941837523657</v>
+        <v>3.36349539977298</v>
       </c>
       <c r="G21">
-        <v>-0.2532943004235117</v>
+        <v>1.210976544323831</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.095146623194224</v>
       </c>
       <c r="E22">
-        <v>-31.30373528346006</v>
+        <v>-28.8103212670447</v>
       </c>
       <c r="F22">
-        <v>4.06909046980357</v>
+        <v>4.092440490153683</v>
       </c>
       <c r="G22">
-        <v>0.4926775470315434</v>
+        <v>1.302489954665904</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.623368101934267</v>
       </c>
       <c r="E23">
-        <v>-31.11989735264467</v>
+        <v>-29.15975190689857</v>
       </c>
       <c r="F23">
-        <v>4.365230159569588</v>
+        <v>3.292370117833809</v>
       </c>
       <c r="G23">
-        <v>0.3040360411127926</v>
+        <v>0.2354084320837009</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-3.309190751032815</v>
       </c>
       <c r="E24">
-        <v>-31.6075121126056</v>
+        <v>-29.01053415987182</v>
       </c>
       <c r="F24">
-        <v>4.353523671433225</v>
+        <v>3.163906901007661</v>
       </c>
       <c r="G24">
-        <v>0.2973454285779256</v>
+        <v>1.910047893124031</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.147573081869557</v>
       </c>
       <c r="E25">
-        <v>-32.48046378282721</v>
+        <v>-29.56374386583385</v>
       </c>
       <c r="F25">
-        <v>4.137170673170051</v>
+        <v>4.010485132790311</v>
       </c>
       <c r="G25">
-        <v>0.3020232294249158</v>
+        <v>1.924104469483776</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.117345051938607</v>
       </c>
       <c r="E26">
-        <v>-32.69385000654265</v>
+        <v>-29.35249281761303</v>
       </c>
       <c r="F26">
-        <v>3.94007887375677</v>
+        <v>3.697097176963202</v>
       </c>
       <c r="G26">
-        <v>0.5581204112518562</v>
+        <v>1.46380621770351</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.195169360178866</v>
       </c>
       <c r="E27">
-        <v>-32.47877919049635</v>
+        <v>-29.1274774726459</v>
       </c>
       <c r="F27">
-        <v>4.201586179146545</v>
+        <v>3.751436421852044</v>
       </c>
       <c r="G27">
-        <v>0.2988451057072154</v>
+        <v>0.5743685687585992</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.345486829785063</v>
       </c>
       <c r="E28">
-        <v>-32.10475440830683</v>
+        <v>-28.43863317744313</v>
       </c>
       <c r="F28">
-        <v>4.289871920202112</v>
+        <v>3.877803869149109</v>
       </c>
       <c r="G28">
-        <v>-0.3390473615272533</v>
+        <v>1.101748404801117</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.542167524084746</v>
       </c>
       <c r="E29">
-        <v>-31.69770799365337</v>
+        <v>-29.24121462582255</v>
       </c>
       <c r="F29">
-        <v>4.170552222768065</v>
+        <v>3.658148998418375</v>
       </c>
       <c r="G29">
-        <v>0.34288529301614</v>
+        <v>0.9918118085329996</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.753656898321681</v>
       </c>
       <c r="E30">
-        <v>-31.76509395112451</v>
+        <v>-27.85346829464597</v>
       </c>
       <c r="F30">
-        <v>4.397987120145892</v>
+        <v>3.665488333607179</v>
       </c>
       <c r="G30">
-        <v>-0.4381518527908755</v>
+        <v>0.01593250501217831</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.965410545670466</v>
       </c>
       <c r="E31">
-        <v>-31.28615121888827</v>
+        <v>-29.32140937202438</v>
       </c>
       <c r="F31">
-        <v>4.351906698262961</v>
+        <v>3.768452745040352</v>
       </c>
       <c r="G31">
-        <v>0.01614437992669166</v>
+        <v>-0.06355369338572289</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.159327223491016</v>
       </c>
       <c r="E32">
-        <v>-30.42283387711798</v>
+        <v>-27.62220818402227</v>
       </c>
       <c r="F32">
-        <v>4.126719990016332</v>
+        <v>3.476946942525594</v>
       </c>
       <c r="G32">
-        <v>-1.21356107118113</v>
+        <v>-0.4454151897040365</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.334068360811702</v>
       </c>
       <c r="E33">
-        <v>-30.09564483735279</v>
+        <v>-28.51528212849696</v>
       </c>
       <c r="F33">
-        <v>4.368179147523555</v>
+        <v>3.871012913180958</v>
       </c>
       <c r="G33">
-        <v>-1.121385551731202</v>
+        <v>-1.301704346164225</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.483760005797143</v>
       </c>
       <c r="E34">
-        <v>-29.49544089237616</v>
+        <v>-26.88515375453384</v>
       </c>
       <c r="F34">
-        <v>3.890186305086156</v>
+        <v>3.698677701967743</v>
       </c>
       <c r="G34">
-        <v>-1.215911558514013</v>
+        <v>-1.447259101889362</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.616333184198911</v>
       </c>
       <c r="E35">
-        <v>-29.39213960755019</v>
+        <v>-26.875213754087</v>
       </c>
       <c r="F35">
-        <v>4.412650879910249</v>
+        <v>3.71140308200955</v>
       </c>
       <c r="G35">
-        <v>-2.182378981066686</v>
+        <v>-1.476345554997398</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.732394263583102</v>
       </c>
       <c r="E36">
-        <v>-29.32530838814499</v>
+        <v>-26.32691517818629</v>
       </c>
       <c r="F36">
-        <v>4.503494619505659</v>
+        <v>4.007105393786889</v>
       </c>
       <c r="G36">
-        <v>-1.337163599435359</v>
+        <v>-1.593916269279075</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.841994691417662</v>
       </c>
       <c r="E37">
-        <v>-28.61064726262449</v>
+        <v>-26.08548864341536</v>
       </c>
       <c r="F37">
-        <v>4.411709854540669</v>
+        <v>3.637685010099616</v>
       </c>
       <c r="G37">
-        <v>-2.356480570976958</v>
+        <v>-2.464291797008863</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.944789835082229</v>
       </c>
       <c r="E38">
-        <v>-27.53413842152109</v>
+        <v>-25.55025471502678</v>
       </c>
       <c r="F38">
-        <v>4.330672328259598</v>
+        <v>3.948831403734749</v>
       </c>
       <c r="G38">
-        <v>-1.910017089005306</v>
+        <v>-1.805903742340766</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.047599088409941</v>
       </c>
       <c r="E39">
-        <v>-28.03808059451667</v>
+        <v>-24.6782653455318</v>
       </c>
       <c r="F39">
-        <v>4.242701366817096</v>
+        <v>3.849031355780271</v>
       </c>
       <c r="G39">
-        <v>-2.318028584538323</v>
+        <v>-1.696629255180503</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.145873849464097</v>
       </c>
       <c r="E40">
-        <v>-27.01228160535117</v>
+        <v>-23.19245490971912</v>
       </c>
       <c r="F40">
-        <v>4.544528627170735</v>
+        <v>4.093979596788085</v>
       </c>
       <c r="G40">
-        <v>-2.883466452100302</v>
+        <v>-2.679692442521543</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.241735166236555</v>
       </c>
       <c r="E41">
-        <v>-26.03653583939245</v>
+        <v>-23.57779634845382</v>
       </c>
       <c r="F41">
-        <v>5.060073020711841</v>
+        <v>3.814274716293609</v>
       </c>
       <c r="G41">
-        <v>-2.457260198283451</v>
+        <v>-2.488611064540349</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.326790445540544</v>
       </c>
       <c r="E42">
-        <v>-25.73599913339939</v>
+        <v>-22.81679081993882</v>
       </c>
       <c r="F42">
-        <v>4.723886737224885</v>
+        <v>4.05253471889122</v>
       </c>
       <c r="G42">
-        <v>-3.079795044761241</v>
+        <v>-3.270320251091837</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.402024586397095</v>
       </c>
       <c r="E43">
-        <v>-25.94932195847872</v>
+        <v>-21.7991883687272</v>
       </c>
       <c r="F43">
-        <v>4.516006280757543</v>
+        <v>3.854853121887146</v>
       </c>
       <c r="G43">
-        <v>-2.54470494815776</v>
+        <v>-2.472866109955576</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.460711657557704</v>
       </c>
       <c r="E44">
-        <v>-24.37325450721917</v>
+        <v>-22.10927562640243</v>
       </c>
       <c r="F44">
-        <v>4.922628644504542</v>
+        <v>4.202767431062938</v>
       </c>
       <c r="G44">
-        <v>-2.726463829900366</v>
+        <v>-2.941040149573767</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.507755439744587</v>
       </c>
       <c r="E45">
-        <v>-24.25013888437264</v>
+        <v>-21.19268984487991</v>
       </c>
       <c r="F45">
-        <v>5.104950653125908</v>
+        <v>3.929303470581154</v>
       </c>
       <c r="G45">
-        <v>-3.120693524353397</v>
+        <v>-2.552918411640692</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.542152101497178</v>
       </c>
       <c r="E46">
-        <v>-23.58003341461361</v>
+        <v>-19.97461184934872</v>
       </c>
       <c r="F46">
-        <v>4.987584246027662</v>
+        <v>4.168782829995686</v>
       </c>
       <c r="G46">
-        <v>-3.869658104975953</v>
+        <v>-3.199272633273538</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.573883342579474</v>
       </c>
       <c r="E47">
-        <v>-23.26750530944824</v>
+        <v>-19.55955003570169</v>
       </c>
       <c r="F47">
-        <v>4.767709029567784</v>
+        <v>3.872074880191347</v>
       </c>
       <c r="G47">
-        <v>-3.509139695749321</v>
+        <v>-3.204526469044361</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.606649530803846</v>
       </c>
       <c r="E48">
-        <v>-22.01455806405799</v>
+        <v>-19.43878469086513</v>
       </c>
       <c r="F48">
-        <v>5.093575511950664</v>
+        <v>4.369975048052824</v>
       </c>
       <c r="G48">
-        <v>-3.923619997266074</v>
+        <v>-3.580342909207966</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.651354978484475</v>
       </c>
       <c r="E49">
-        <v>-22.26952020763785</v>
+        <v>-18.89715655717772</v>
       </c>
       <c r="F49">
-        <v>5.066073714177721</v>
+        <v>4.123623552664667</v>
       </c>
       <c r="G49">
-        <v>-4.188218660037863</v>
+        <v>-3.782637104930671</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.712683228939424</v>
       </c>
       <c r="E50">
-        <v>-21.94979182880029</v>
+        <v>-18.29596993334142</v>
       </c>
       <c r="F50">
-        <v>4.917231002507901</v>
+        <v>4.237871984858775</v>
       </c>
       <c r="G50">
-        <v>-4.038154941288239</v>
+        <v>-3.743410450835846</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.797959956128614</v>
       </c>
       <c r="E51">
-        <v>-21.59334205423454</v>
+        <v>-18.30999914581719</v>
       </c>
       <c r="F51">
-        <v>5.024534402396937</v>
+        <v>4.291505460720432</v>
       </c>
       <c r="G51">
-        <v>-3.970583396286175</v>
+        <v>-3.57028216131412</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.910058402460002</v>
       </c>
       <c r="E52">
-        <v>-20.22222880808814</v>
+        <v>-17.8762483199405</v>
       </c>
       <c r="F52">
-        <v>4.975707114206323</v>
+        <v>3.999204425498987</v>
       </c>
       <c r="G52">
-        <v>-4.370851525802836</v>
+        <v>-3.942721845027668</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.050543786053549</v>
       </c>
       <c r="E53">
-        <v>-20.13916753783944</v>
+        <v>-16.44939408723369</v>
       </c>
       <c r="F53">
-        <v>5.089354151665998</v>
+        <v>4.179639413176775</v>
       </c>
       <c r="G53">
-        <v>-4.540788449424705</v>
+        <v>-3.948571578995561</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.220853259272504</v>
       </c>
       <c r="E54">
-        <v>-18.87392095704436</v>
+        <v>-15.8642110905405</v>
       </c>
       <c r="F54">
-        <v>4.879064802791316</v>
+        <v>4.517414505342302</v>
       </c>
       <c r="G54">
-        <v>-5.250870672688521</v>
+        <v>-4.643203486227598</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.417200964637975</v>
       </c>
       <c r="E55">
-        <v>-19.55349546595343</v>
+        <v>-16.01215180789708</v>
       </c>
       <c r="F55">
-        <v>4.715506972578165</v>
+        <v>4.455888344866771</v>
       </c>
       <c r="G55">
-        <v>-5.768398325206167</v>
+        <v>-5.203576219114493</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.640187661590745</v>
       </c>
       <c r="E56">
-        <v>-17.9890707213676</v>
+        <v>-15.0714428453357</v>
       </c>
       <c r="F56">
-        <v>4.986525592486885</v>
+        <v>4.481605839254085</v>
       </c>
       <c r="G56">
-        <v>-5.314403352132675</v>
+        <v>-5.627494885963707</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.882129862218741</v>
       </c>
       <c r="E57">
-        <v>-18.65940261482701</v>
+        <v>-14.75744298611785</v>
       </c>
       <c r="F57">
-        <v>4.564131113390583</v>
+        <v>4.074375453833431</v>
       </c>
       <c r="G57">
-        <v>-5.877772128732609</v>
+        <v>-5.169888107706869</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.145133032589733</v>
       </c>
       <c r="E58">
-        <v>-18.11704539682436</v>
+        <v>-15.03230777296142</v>
       </c>
       <c r="F58">
-        <v>5.157366428905449</v>
+        <v>4.276006706614053</v>
       </c>
       <c r="G58">
-        <v>-5.962561821084423</v>
+        <v>-6.090898429459809</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.419149674738985</v>
       </c>
       <c r="E59">
-        <v>-17.52602519713529</v>
+        <v>-13.94015758263552</v>
       </c>
       <c r="F59">
-        <v>4.864570029977131</v>
+        <v>4.171528039568563</v>
       </c>
       <c r="G59">
-        <v>-6.230563724670582</v>
+        <v>-5.908060309871401</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.708289198359021</v>
       </c>
       <c r="E60">
-        <v>-16.99453178827704</v>
+        <v>-13.20904903951917</v>
       </c>
       <c r="F60">
-        <v>4.844178937989818</v>
+        <v>4.088427878454522</v>
       </c>
       <c r="G60">
-        <v>-6.885939182897943</v>
+        <v>-5.89938999110405</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.000321864003947</v>
       </c>
       <c r="E61">
-        <v>-17.25390013706636</v>
+        <v>-14.46441449002951</v>
       </c>
       <c r="F61">
-        <v>4.633011519668168</v>
+        <v>4.312541022547123</v>
       </c>
       <c r="G61">
-        <v>-7.016152870594095</v>
+        <v>-6.583580437705226</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.299860244503483</v>
       </c>
       <c r="E62">
-        <v>-16.97487821108375</v>
+        <v>-13.27576704707418</v>
       </c>
       <c r="F62">
-        <v>4.897570530569856</v>
+        <v>4.119806435672568</v>
       </c>
       <c r="G62">
-        <v>-7.14772388196135</v>
+        <v>-6.657216902135235</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.59199475980196</v>
       </c>
       <c r="E63">
-        <v>-16.82906134803677</v>
+        <v>-12.58695445118946</v>
       </c>
       <c r="F63">
-        <v>4.519675948351945</v>
+        <v>3.924896555998261</v>
       </c>
       <c r="G63">
-        <v>-7.250546115865575</v>
+        <v>-6.874617117153635</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.878944133488723</v>
       </c>
       <c r="E64">
-        <v>-15.59350797130998</v>
+        <v>-12.63500608888485</v>
       </c>
       <c r="F64">
-        <v>4.409120378039518</v>
+        <v>3.601004901503654</v>
       </c>
       <c r="G64">
-        <v>-7.211246629768886</v>
+        <v>-6.227653755141563</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.144460243084579</v>
       </c>
       <c r="E65">
-        <v>-15.14871672580259</v>
+        <v>-12.65809677784996</v>
       </c>
       <c r="F65">
-        <v>4.480603514696698</v>
+        <v>3.653998877730349</v>
       </c>
       <c r="G65">
-        <v>-7.357274793506138</v>
+        <v>-7.043176853831167</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.391170167973494</v>
       </c>
       <c r="E66">
-        <v>-15.79788253175015</v>
+        <v>-12.0598219628006</v>
       </c>
       <c r="F66">
-        <v>4.553743386159478</v>
+        <v>3.907131388677823</v>
       </c>
       <c r="G66">
-        <v>-7.501114686641932</v>
+        <v>-6.554179482770959</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.6045092348353</v>
       </c>
       <c r="E67">
-        <v>-14.71559535781297</v>
+        <v>-12.59326714395615</v>
       </c>
       <c r="F67">
-        <v>4.357692016204113</v>
+        <v>3.351550341824611</v>
       </c>
       <c r="G67">
-        <v>-7.492199387504675</v>
+        <v>-6.523725774355203</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.78804472270768</v>
       </c>
       <c r="E68">
-        <v>-15.36983305464912</v>
+        <v>-11.58250721697012</v>
       </c>
       <c r="F68">
-        <v>4.213933823652675</v>
+        <v>3.733666284327189</v>
       </c>
       <c r="G68">
-        <v>-8.200464121267432</v>
+        <v>-6.414060642821306</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.927555198697091</v>
       </c>
       <c r="E69">
-        <v>-14.72710673874046</v>
+        <v>-11.08676158192842</v>
       </c>
       <c r="F69">
-        <v>4.157570048831391</v>
+        <v>3.947592166100161</v>
       </c>
       <c r="G69">
-        <v>-7.895284791275256</v>
+        <v>-6.909331497678433</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.02710261137078</v>
       </c>
       <c r="E70">
-        <v>-15.2241746881924</v>
+        <v>-13.05097812580743</v>
       </c>
       <c r="F70">
-        <v>4.08304183360152</v>
+        <v>3.391583681667105</v>
       </c>
       <c r="G70">
-        <v>-7.961482459878523</v>
+        <v>-7.039849755564199</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.07429062671115</v>
       </c>
       <c r="E71">
-        <v>-14.42214571364192</v>
+        <v>-12.52183499495916</v>
       </c>
       <c r="F71">
-        <v>3.972297395521254</v>
+        <v>3.261031322251098</v>
       </c>
       <c r="G71">
-        <v>-7.92647344080073</v>
+        <v>-6.611988228977713</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.07589544742794</v>
       </c>
       <c r="E72">
-        <v>-15.34425623345379</v>
+        <v>-12.81865382379191</v>
       </c>
       <c r="F72">
-        <v>4.139412235362026</v>
+        <v>3.022444942896784</v>
       </c>
       <c r="G72">
-        <v>-7.625184001817198</v>
+        <v>-6.584166404265678</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.02241474389452</v>
       </c>
       <c r="E73">
-        <v>-15.11629738038168</v>
+        <v>-11.72823803901096</v>
       </c>
       <c r="F73">
-        <v>4.2523783548166</v>
+        <v>3.085957528404228</v>
       </c>
       <c r="G73">
-        <v>-7.296728226138407</v>
+        <v>-6.669055412983669</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.92209907201482</v>
       </c>
       <c r="E74">
-        <v>-14.6770625724817</v>
+        <v>-11.86373450979447</v>
       </c>
       <c r="F74">
-        <v>4.072069278984038</v>
+        <v>2.951465453620505</v>
       </c>
       <c r="G74">
-        <v>-6.740523470085455</v>
+        <v>-5.739887907021965</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.766652013290384</v>
       </c>
       <c r="E75">
-        <v>-15.3022818078767</v>
+        <v>-11.34550500130469</v>
       </c>
       <c r="F75">
-        <v>3.588196684721568</v>
+        <v>3.088982726159252</v>
       </c>
       <c r="G75">
-        <v>-6.768007619152485</v>
+        <v>-6.905951430682837</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.566421188794417</v>
       </c>
       <c r="E76">
-        <v>-16.06993060776095</v>
+        <v>-13.79573096110889</v>
       </c>
       <c r="F76">
-        <v>3.677720006676916</v>
+        <v>3.2306434924468</v>
       </c>
       <c r="G76">
-        <v>-6.436724637583156</v>
+        <v>-7.066459920608861</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.31557859703998</v>
       </c>
       <c r="E77">
-        <v>-15.46009912704401</v>
+        <v>-13.4242058965716</v>
       </c>
       <c r="F77">
-        <v>3.667804448865406</v>
+        <v>2.976099443444957</v>
       </c>
       <c r="G77">
-        <v>-6.531015595632678</v>
+        <v>-5.50056856998805</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.027059206854815</v>
       </c>
       <c r="E78">
-        <v>-15.6928808049343</v>
+        <v>-13.03223024341567</v>
       </c>
       <c r="F78">
-        <v>3.576377538618424</v>
+        <v>2.825152678572026</v>
       </c>
       <c r="G78">
-        <v>-6.491593619351037</v>
+        <v>-5.868135130667791</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.697509444569343</v>
       </c>
       <c r="E79">
-        <v>-16.44744684341039</v>
+        <v>-13.06322311952417</v>
       </c>
       <c r="F79">
-        <v>3.689694885851786</v>
+        <v>2.730448746879569</v>
       </c>
       <c r="G79">
-        <v>-5.984805376562786</v>
+        <v>-6.22693867730508</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.34208277208192</v>
       </c>
       <c r="E80">
-        <v>-17.1353718583896</v>
+        <v>-14.08306263689558</v>
       </c>
       <c r="F80">
-        <v>3.740172281908777</v>
+        <v>2.786867193949438</v>
       </c>
       <c r="G80">
-        <v>-6.285952462088129</v>
+        <v>-5.212064457877184</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.95988971043342</v>
       </c>
       <c r="E81">
-        <v>-17.69653130047209</v>
+        <v>-14.42091849718584</v>
       </c>
       <c r="F81">
-        <v>3.648584668385652</v>
+        <v>2.73428077448492</v>
       </c>
       <c r="G81">
-        <v>-5.695874204077354</v>
+        <v>-4.243402143631974</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.56620592566915</v>
       </c>
       <c r="E82">
-        <v>-18.47167925331305</v>
+        <v>-15.61201584457933</v>
       </c>
       <c r="F82">
-        <v>3.575287407116341</v>
+        <v>2.515338299720594</v>
       </c>
       <c r="G82">
-        <v>-5.248023603524747</v>
+        <v>-4.668744345063075</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.161538563956497</v>
       </c>
       <c r="E83">
-        <v>-18.05740992261735</v>
+        <v>-15.0445210673601</v>
       </c>
       <c r="F83">
-        <v>3.373170731037678</v>
+        <v>2.756789173553788</v>
       </c>
       <c r="G83">
-        <v>-5.381031391656046</v>
+        <v>-4.633728704894204</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.758236690377579</v>
       </c>
       <c r="E84">
-        <v>-20.40948573677931</v>
+        <v>-15.69892178926053</v>
       </c>
       <c r="F84">
-        <v>3.722347472135337</v>
+        <v>2.894636136318848</v>
       </c>
       <c r="G84">
-        <v>-4.506441539454766</v>
+        <v>-4.854224279991822</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.357387735605806</v>
       </c>
       <c r="E85">
-        <v>-20.14719652225504</v>
+        <v>-17.42638065507051</v>
       </c>
       <c r="F85">
-        <v>3.642744678195915</v>
+        <v>2.54637391283388</v>
       </c>
       <c r="G85">
-        <v>-4.284181443584717</v>
+        <v>-3.621555890626353</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.967864092976565</v>
       </c>
       <c r="E86">
-        <v>-21.62170388694458</v>
+        <v>-18.56838481574684</v>
       </c>
       <c r="F86">
-        <v>3.394353742262067</v>
+        <v>2.324858528916459</v>
       </c>
       <c r="G86">
-        <v>-4.169762368656426</v>
+        <v>-3.556079920950647</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.59134827894254</v>
       </c>
       <c r="E87">
-        <v>-21.94608753706202</v>
+        <v>-20.19735842883801</v>
       </c>
       <c r="F87">
-        <v>3.483679912775549</v>
+        <v>2.572956222789716</v>
       </c>
       <c r="G87">
-        <v>-4.359569186604999</v>
+        <v>-4.459405308432801</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.23384565396506</v>
       </c>
       <c r="E88">
-        <v>-24.32359978972506</v>
+        <v>-21.52704972323625</v>
       </c>
       <c r="F88">
-        <v>2.893918770148024</v>
+        <v>2.659253882078563</v>
       </c>
       <c r="G88">
-        <v>-3.870416219904446</v>
+        <v>-3.704670446935295</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.897685054025687</v>
       </c>
       <c r="E89">
-        <v>-24.89363504086259</v>
+        <v>-22.6907316889873</v>
       </c>
       <c r="F89">
-        <v>3.073286820611007</v>
+        <v>2.430110891116164</v>
       </c>
       <c r="G89">
-        <v>-4.27021756250007</v>
+        <v>-3.785497416276601</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.586439911081175</v>
       </c>
       <c r="E90">
-        <v>-26.67592014148344</v>
+        <v>-23.63066628249337</v>
       </c>
       <c r="F90">
-        <v>2.917767467674622</v>
+        <v>2.069103406771723</v>
       </c>
       <c r="G90">
-        <v>-3.083403539399046</v>
+        <v>-3.052873688435887</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.304041715746193</v>
       </c>
       <c r="E91">
-        <v>-27.97236337971736</v>
+        <v>-25.6783199599637</v>
       </c>
       <c r="F91">
-        <v>2.822031390198277</v>
+        <v>2.457905930949698</v>
       </c>
       <c r="G91">
-        <v>-3.457700439160125</v>
+        <v>-3.42992496208564</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.052557986176171</v>
       </c>
       <c r="E92">
-        <v>-28.98598077380223</v>
+        <v>-26.98780520333971</v>
       </c>
       <c r="F92">
-        <v>2.494986969368616</v>
+        <v>2.206211465813486</v>
       </c>
       <c r="G92">
-        <v>-3.241948875820283</v>
+        <v>-2.960674995167185</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.837179310302795</v>
       </c>
       <c r="E93">
-        <v>-31.18293144659444</v>
+        <v>-28.29376729393776</v>
       </c>
       <c r="F93">
-        <v>2.225186049542011</v>
+        <v>1.951640909054753</v>
       </c>
       <c r="G93">
-        <v>-3.531803690511171</v>
+        <v>-3.293149773130651</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.657512480897661</v>
       </c>
       <c r="E94">
-        <v>-32.74875548964864</v>
+        <v>-30.72010555335151</v>
       </c>
       <c r="F94">
-        <v>2.29638754128224</v>
+        <v>1.435770138756944</v>
       </c>
       <c r="G94">
-        <v>-3.088796418082519</v>
+        <v>-2.931128376229189</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.516834035309659</v>
       </c>
       <c r="E95">
-        <v>-34.11253940061363</v>
+        <v>-32.433700495987</v>
       </c>
       <c r="F95">
-        <v>1.72767521435985</v>
+        <v>1.293001016884449</v>
       </c>
       <c r="G95">
-        <v>-3.477169757476579</v>
+        <v>-2.552454935265194</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.413338869523043</v>
       </c>
       <c r="E96">
-        <v>-36.16403322404246</v>
+        <v>-34.70689934988336</v>
       </c>
       <c r="F96">
-        <v>1.612078200033985</v>
+        <v>1.310693287873441</v>
       </c>
       <c r="G96">
-        <v>-4.011617608245441</v>
+        <v>-2.809929304036471</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.34598573782946</v>
       </c>
       <c r="E97">
-        <v>-38.21107329328476</v>
+        <v>-36.54602359201148</v>
       </c>
       <c r="F97">
-        <v>1.140891224177987</v>
+        <v>0.6050650831467379</v>
       </c>
       <c r="G97">
-        <v>-3.148488864701118</v>
+        <v>-2.95760611945228</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.314654475926853</v>
       </c>
       <c r="E98">
-        <v>-41.23674376642865</v>
+        <v>-40.14763897487292</v>
       </c>
       <c r="F98">
-        <v>0.762136796595969</v>
+        <v>0.3773286600342923</v>
       </c>
       <c r="G98">
-        <v>-4.187589656385401</v>
+        <v>-3.076464635948734</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.311443719742882</v>
       </c>
       <c r="E99">
-        <v>-42.87566417267767</v>
+        <v>-41.57363279751828</v>
       </c>
       <c r="F99">
-        <v>0.4221391946887315</v>
+        <v>0.07685412364942477</v>
       </c>
       <c r="G99">
-        <v>-4.50319720482628</v>
+        <v>-3.410045136122316</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.343713111460834</v>
       </c>
       <c r="E100">
-        <v>-45.65489735456115</v>
+        <v>-44.79794478300864</v>
       </c>
       <c r="F100">
-        <v>0.2116916276401143</v>
+        <v>-0.1507804102724766</v>
       </c>
       <c r="G100">
-        <v>-4.090130506254797</v>
+        <v>-3.428402111137575</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.390563362939309</v>
       </c>
       <c r="E101">
-        <v>-47.54071016370835</v>
+        <v>-45.68471962013866</v>
       </c>
       <c r="F101">
-        <v>-0.0672726923962584</v>
+        <v>-0.7529819745552444</v>
       </c>
       <c r="G101">
-        <v>-4.069088678807189</v>
+        <v>-3.858418802870128</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.484725565590882</v>
       </c>
       <c r="E102">
-        <v>-50.40029658838393</v>
+        <v>-48.32169984801919</v>
       </c>
       <c r="F102">
-        <v>-0.7023223376696378</v>
+        <v>-0.8914154214414866</v>
       </c>
       <c r="G102">
-        <v>-4.23015665092935</v>
+        <v>-3.871041913011369</v>
       </c>
     </row>
   </sheetData>
